--- a/VerveStacks_IND_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4B6226-1EEF-4319-88D1-F7679D25B5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0762234-8F09-4B3B-BB0B-0DC2B2932C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9161,7 +9161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B903AF-2742-40CA-8C7F-FAE16237664D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F42D25-EBEC-418B-91C0-09F95657CAB4}">
   <dimension ref="B3:H183"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0762234-8F09-4B3B-BB0B-0DC2B2932C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C1C6F6-5FCC-4368-AE03-119C27F82794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9161,7 +9161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F42D25-EBEC-418B-91C0-09F95657CAB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8D81BD-EC6F-4F67-B3B2-2CF946587AAD}">
   <dimension ref="B3:H183"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C1C6F6-5FCC-4368-AE03-119C27F82794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEC5303-835E-43D8-BEC3-BDA0178D48CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9161,7 +9161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8D81BD-EC6F-4F67-B3B2-2CF946587AAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660D5C79-61FC-4081-8078-4174FA78C000}">
   <dimension ref="B3:H183"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
